--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>6.156257</v>
+        <v>5.686143</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>5.686143</v>
+        <v>7.141258</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>7.141258</v>
+        <v>6.626371</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>6.626371</v>
+        <v>7.118872</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>7.118872</v>
+        <v>6.335348</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>6.335348</v>
+        <v>7.051713</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>7.051713</v>
+        <v>7.00694</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>7.857623</v>
+        <v>7.00694</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>7.857623</v>
+        <v>7.723304</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>7.723304</v>
+        <v>9.245578999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>9.245578999999999</v>
+        <v>9.827624999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>9.827624999999999</v>
+        <v>9.872398</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>9.872398</v>
+        <v>11.394672</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>11.394672</v>
+        <v>11.708081</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>11.708081</v>
+        <v>11.752854</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>11.752854</v>
+        <v>12.245355</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>12.245355</v>
+        <v>9.267965</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>9.267965</v>
+        <v>8.215805</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>8.215805</v>
+        <v>8.148645999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>8.148645999999999</v>
+        <v>6.850235</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,482 +434,474 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B2" t="n">
-        <v>-8.199329000000001</v>
+        <v>-3.291627</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B3" t="n">
-        <v>-3.291627</v>
+        <v>-1.612261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.612261</v>
+        <v>-1.497067</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.497067</v>
+        <v>9.159992000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B6" t="n">
-        <v>9.159992000000001</v>
+        <v>12.173095</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B7" t="n">
-        <v>12.173095</v>
+        <v>10.31533</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B8" t="n">
-        <v>10.31533</v>
+        <v>-1.581268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.581268</v>
+        <v>5.561563</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B10" t="n">
-        <v>5.561563</v>
+        <v>-1.463486</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.463486</v>
+        <v>-0.490123</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.490123</v>
+        <v>-2.268657</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B13" t="n">
-        <v>-2.268657</v>
+        <v>-7.910812</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B14" t="n">
-        <v>-7.910812</v>
+        <v>-9.46932</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B15" t="n">
-        <v>-9.46932</v>
+        <v>3.095805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B16" t="n">
-        <v>3.095805</v>
+        <v>4.442075</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B17" t="n">
-        <v>4.442075</v>
+        <v>3.385505</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B18" t="n">
-        <v>3.385505</v>
+        <v>1.234162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B19" t="n">
-        <v>1.234162</v>
+        <v>-3.088427</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B20" t="n">
-        <v>-3.088427</v>
+        <v>1.006374</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B21" t="n">
-        <v>1.006374</v>
+        <v>-4.068416</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B22" t="n">
-        <v>-4.068416</v>
+        <v>-10.005193</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B23" t="n">
-        <v>-10.005193</v>
+        <v>19.811502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B24" t="n">
-        <v>19.811502</v>
+        <v>-7.160058</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B25" t="n">
-        <v>-7.160058</v>
+        <v>-5.931178</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B26" t="n">
-        <v>-5.931178</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B27" t="n">
-        <v>-6.25</v>
+        <v>0.941176</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B28" t="n">
-        <v>0.941176</v>
+        <v>4.331779</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B29" t="n">
-        <v>4.331779</v>
+        <v>-3.667846</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B30" t="n">
-        <v>-3.667846</v>
+        <v>-5.508311</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B31" t="n">
-        <v>-5.508311</v>
+        <v>-7.690734</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B32" t="n">
-        <v>-7.690734</v>
+        <v>5.606027</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B33" t="n">
-        <v>5.606027</v>
+        <v>-3.86068</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B34" t="n">
-        <v>-3.86068</v>
+        <v>5.194238</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B35" t="n">
-        <v>5.194238</v>
+        <v>-4.522822</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B36" t="n">
-        <v>-4.522822</v>
+        <v>-10.604085</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B37" t="n">
-        <v>-10.604085</v>
+        <v>-4.521147</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B38" t="n">
-        <v>-4.521147</v>
+        <v>7.637475</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B39" t="n">
-        <v>7.637475</v>
+        <v>-7.04825</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B40" t="n">
-        <v>-7.04825</v>
+        <v>0.712468</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B41" t="n">
-        <v>0.712468</v>
+        <v>0.884285</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>0.884285</v>
+        <v>4.38267</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B43" t="n">
-        <v>4.38267</v>
+        <v>-2.927063</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B44" t="n">
-        <v>-2.927063</v>
+        <v>0.321305</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B45" t="n">
-        <v>0.321305</v>
+        <v>1.970929</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B46" t="n">
-        <v>1.970929</v>
+        <v>0.676492</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B47" t="n">
-        <v>0.676492</v>
+        <v>-1.679866</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.679866</v>
+        <v>-6.102026</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B49" t="n">
-        <v>-6.102026</v>
+        <v>7.798284</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B50" t="n">
-        <v>7.798284</v>
+        <v>-3.375934</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B51" t="n">
-        <v>-3.375934</v>
+        <v>9.78288</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B52" t="n">
-        <v>9.78288</v>
+        <v>3.455331</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B53" t="n">
-        <v>3.455331</v>
+        <v>-9.426500000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B54" t="n">
-        <v>-9.426500000000001</v>
+        <v>3.275109</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B55" t="n">
-        <v>3.275109</v>
+        <v>8.738548</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B56" t="n">
-        <v>8.738548</v>
+        <v>1.188162</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B57" t="n">
-        <v>1.188162</v>
+        <v>0.939368</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B58" t="n">
-        <v>0.939368</v>
+        <v>0.401861</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B59" t="n">
-        <v>0.401861</v>
+        <v>-5.898462</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B60" t="n">
-        <v>-5.898462</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B61" t="n">
-        <v>6.850235</v>
+        <v>6.424894</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -901,7 +901,7 @@
         <v>46234</v>
       </c>
       <c r="B60" t="n">
-        <v>6.424894</v>
+        <v>4.947392</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -901,7 +901,7 @@
         <v>46234</v>
       </c>
       <c r="B60" t="n">
-        <v>4.947392</v>
+        <v>6.335348</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,7 +901,15 @@
         <v>46234</v>
       </c>
       <c r="B60" t="n">
-        <v>6.335348</v>
+        <v>4.947392</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.661263</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.661263</v>
+        <v>0.874573</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.874573</v>
+        <v>-0.362628</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.362628</v>
+        <v>0.170648</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.170648</v>
+        <v>0.874573</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.874573</v>
+        <v>-1.322526</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.322526</v>
+        <v>0.362628</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.362628</v>
+        <v>0.959898</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.959898</v>
+        <v>0.746587</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.746587</v>
+        <v>0.277304</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.277304</v>
+        <v>1.066553</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>1.066553</v>
+        <v>1.237201</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>1.237201</v>
+        <v>0.149317</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>0.149317</v>
+        <v>1.749147</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>1.749147</v>
+        <v>2.282423</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>2.282423</v>
+        <v>4.522184</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>4.522184</v>
+        <v>4.714164</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>4.714164</v>
+        <v>5.930034</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>5.930034</v>
+        <v>5.098123</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>5.098123</v>
+        <v>4.522184</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>4.522184</v>
+        <v>5.759386</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>5.759386</v>
+        <v>5.567406</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>5.567406</v>
+        <v>3.946246</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>3.946246</v>
+        <v>5.866041</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>5.866041</v>
+        <v>7.807167</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>7.807167</v>
+        <v>9.87628</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>9.87628</v>
+        <v>7.209898</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>7.209898</v>
+        <v>9.897610999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>9.897610999999999</v>
+        <v>10.068259</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -434,482 +434,482 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.291627</v>
+        <v>-1.612261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.612261</v>
+        <v>-1.497067</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.497067</v>
+        <v>9.159992000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>9.159992000000001</v>
+        <v>12.173095</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>12.173095</v>
+        <v>10.31533</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>10.31533</v>
+        <v>-1.581268</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.581268</v>
+        <v>5.561563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>5.561563</v>
+        <v>-1.463486</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.463486</v>
+        <v>-0.490123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.490123</v>
+        <v>-2.268657</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>-2.268657</v>
+        <v>-7.910812</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>-7.910812</v>
+        <v>-9.46932</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>-9.46932</v>
+        <v>3.095805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>3.095805</v>
+        <v>4.442075</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>4.442075</v>
+        <v>3.385505</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>3.385505</v>
+        <v>1.234162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>1.234162</v>
+        <v>-3.088427</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>-3.088427</v>
+        <v>1.006374</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>1.006374</v>
+        <v>-4.068416</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>-4.068416</v>
+        <v>-10.005193</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>-10.005193</v>
+        <v>19.811502</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>19.811502</v>
+        <v>-7.160058</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>-7.160058</v>
+        <v>-5.931178</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>-5.931178</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>-6.25</v>
+        <v>0.941176</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>0.941176</v>
+        <v>4.331779</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>4.331779</v>
+        <v>-3.667846</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>-3.667846</v>
+        <v>-5.508311</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>-5.508311</v>
+        <v>-7.690734</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>-7.690734</v>
+        <v>5.606027</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>5.606027</v>
+        <v>-3.86068</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>-3.86068</v>
+        <v>5.194238</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>5.194238</v>
+        <v>-4.522822</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>-4.522822</v>
+        <v>-10.604085</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>-10.604085</v>
+        <v>-4.521147</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>-4.521147</v>
+        <v>7.637475</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>7.637475</v>
+        <v>-7.04825</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>-7.04825</v>
+        <v>0.712468</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>0.712468</v>
+        <v>0.884285</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>0.884285</v>
+        <v>4.38267</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>4.38267</v>
+        <v>-2.927063</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>-2.927063</v>
+        <v>0.321305</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>0.321305</v>
+        <v>1.970929</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>1.970929</v>
+        <v>0.676492</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>0.676492</v>
+        <v>-1.679866</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.679866</v>
+        <v>-6.102026</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>-6.102026</v>
+        <v>7.798284</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>7.798284</v>
+        <v>-3.375934</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>-3.375934</v>
+        <v>9.78288</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>9.78288</v>
+        <v>3.455331</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>3.455331</v>
+        <v>-9.426500000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>-9.426500000000001</v>
+        <v>3.275109</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>3.275109</v>
+        <v>8.738548</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>8.738548</v>
+        <v>1.188162</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>1.188162</v>
+        <v>0.939368</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>0.939368</v>
+        <v>0.401861</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>0.401861</v>
+        <v>-5.898462</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B59" t="n">
-        <v>-5.898462</v>
+        <v>4.947392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B60" t="n">
-        <v>4.947392</v>
+        <v>8.809727000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>10.068259</v>
+        <v>2.881788</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.881788</v>
+        <v>2.25446</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.25446</v>
+        <v>1.352676</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>1.352676</v>
+        <v>2.489708</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.489708</v>
+        <v>1.450696</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_soja.xlsx
+++ b/data/final/series/yahoo_ret_soja.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>1.450696</v>
+        <v>2.705352</v>
       </c>
     </row>
   </sheetData>
